--- a/reports/Debug-snowbowl-20260105/Month to Date (Actual)_Visits.xlsx
+++ b/reports/Debug-snowbowl-20260105/Month to Date (Actual)_Visits.xlsx
@@ -31,10 +31,10 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Snowbowl Passes</t>
+    <t>Snowbowl Comp Tickets</t>
   </si>
   <si>
-    <t>Snowbowl Comp Tickets</t>
+    <t>Snowbowl Passes</t>
   </si>
   <si>
     <t>Snowbowl Uplift Tickets</t>
@@ -431,10 +431,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C2" s="2">
-        <v>10</v>
+        <v>631</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -445,13 +445,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>46023</v>
+        <v>46027</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -459,13 +459,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="2">
-        <v>46023</v>
+        <v>46027</v>
       </c>
       <c r="C4" s="2">
-        <v>511</v>
+        <v>368</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -473,10 +473,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="2">
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="C5" s="2">
-        <v>324</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>6</v>
@@ -490,10 +490,10 @@
         <v>46023</v>
       </c>
       <c r="C6" s="2">
-        <v>374</v>
+        <v>14</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -501,13 +501,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="2">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C7" s="2">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -518,10 +518,10 @@
         <v>46024</v>
       </c>
       <c r="C8" s="2">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -529,13 +529,13 @@
         <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="C9" s="2">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -543,10 +543,10 @@
         <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="C10" s="2">
-        <v>539</v>
+        <v>378</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>7</v>
@@ -557,13 +557,13 @@
         <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>46027</v>
+        <v>46023</v>
       </c>
       <c r="C11" s="2">
-        <v>32</v>
+        <v>652</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -571,10 +571,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="2">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="C12" s="2">
-        <v>631</v>
+        <v>19</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>6</v>
@@ -585,13 +585,13 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>46027</v>
+        <v>46025</v>
       </c>
       <c r="C13" s="2">
-        <v>1</v>
+        <v>1917</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -599,10 +599,10 @@
         <v>1</v>
       </c>
       <c r="B14" s="2">
-        <v>46027</v>
+        <v>46025</v>
       </c>
       <c r="C14" s="2">
-        <v>368</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>6</v>
@@ -613,13 +613,13 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>46027</v>
+        <v>46023</v>
       </c>
       <c r="C15" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -630,10 +630,10 @@
         <v>46023</v>
       </c>
       <c r="C16" s="2">
-        <v>652</v>
+        <v>1</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -641,10 +641,10 @@
         <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C17" s="2">
-        <v>19</v>
+        <v>511</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>5</v>
@@ -655,13 +655,13 @@
         <v>1</v>
       </c>
       <c r="B18" s="2">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="C18" s="2">
-        <v>1917</v>
+        <v>324</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -669,13 +669,13 @@
         <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C19" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -683,13 +683,13 @@
         <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="C20" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -697,13 +697,13 @@
         <v>1</v>
       </c>
       <c r="B21" s="2">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="C21" s="2">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -711,13 +711,13 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="C22" s="2">
-        <v>13</v>
+        <v>551</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -728,10 +728,10 @@
         <v>46026</v>
       </c>
       <c r="C23" s="2">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -739,13 +739,13 @@
         <v>1</v>
       </c>
       <c r="B24" s="2">
-        <v>46027</v>
+        <v>46026</v>
       </c>
       <c r="C24" s="2">
-        <v>378</v>
+        <v>658</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -759,7 +759,7 @@
         <v>2</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -773,7 +773,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -787,7 +787,7 @@
         <v>987</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -815,7 +815,7 @@
         <v>1</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -829,7 +829,7 @@
         <v>2</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -843,7 +843,7 @@
         <v>566</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -857,7 +857,7 @@
         <v>3</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -871,7 +871,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -885,7 +885,7 @@
         <v>550</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -913,7 +913,7 @@
         <v>2</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -941,7 +941,7 @@
         <v>15</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -969,7 +969,7 @@
         <v>52</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -983,7 +983,7 @@
         <v>844</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -997,7 +997,7 @@
         <v>1</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1011,7 +1011,7 @@
         <v>2</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1039,7 +1039,7 @@
         <v>7</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1050,10 +1050,10 @@
         <v>46023</v>
       </c>
       <c r="C46" s="2">
-        <v>8</v>
+        <v>374</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1061,13 +1061,13 @@
         <v>1</v>
       </c>
       <c r="B47" s="2">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C47" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1075,13 +1075,13 @@
         <v>1</v>
       </c>
       <c r="B48" s="2">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C48" s="2">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1092,10 +1092,10 @@
         <v>46025</v>
       </c>
       <c r="C49" s="2">
-        <v>551</v>
+        <v>5</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1106,10 +1106,10 @@
         <v>46026</v>
       </c>
       <c r="C50" s="2">
-        <v>11</v>
+        <v>539</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1117,13 +1117,13 @@
         <v>1</v>
       </c>
       <c r="B51" s="2">
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="C51" s="2">
-        <v>658</v>
+        <v>32</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
